--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_05.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_05.xlsx
@@ -480,25 +480,25 @@
         <v>45778</v>
       </c>
       <c r="B5" t="n">
-        <v>1461.93</v>
+        <v>1327.08</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23.62</v>
       </c>
       <c r="D5" t="n">
-        <v>1057.82</v>
+        <v>966.12</v>
       </c>
       <c r="E5" t="n">
-        <v>287.12</v>
+        <v>264.98</v>
       </c>
       <c r="F5" t="n">
-        <v>2573</v>
+        <v>1162</v>
       </c>
       <c r="G5" t="n">
-        <v>389993</v>
+        <v>339259</v>
       </c>
       <c r="H5" t="n">
-        <v>69910</v>
+        <v>59529</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45779</v>
       </c>
       <c r="B6" t="n">
-        <v>1474.49</v>
+        <v>1537.91</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1066.48</v>
+        <v>1109.92</v>
       </c>
       <c r="E6" t="n">
-        <v>303.22</v>
+        <v>298.53</v>
       </c>
       <c r="F6" t="n">
-        <v>2132</v>
+        <v>1426</v>
       </c>
       <c r="G6" t="n">
-        <v>410416</v>
+        <v>381251</v>
       </c>
       <c r="H6" t="n">
-        <v>68700</v>
+        <v>73295</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45780</v>
       </c>
       <c r="B7" t="n">
-        <v>1531.49</v>
+        <v>1468.48</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1105.7</v>
+        <v>1070.93</v>
       </c>
       <c r="E7" t="n">
-        <v>303.25</v>
+        <v>290.08</v>
       </c>
       <c r="F7" t="n">
-        <v>2685</v>
+        <v>1122</v>
       </c>
       <c r="G7" t="n">
-        <v>397240</v>
+        <v>368219</v>
       </c>
       <c r="H7" t="n">
-        <v>65185</v>
+        <v>68992</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45781</v>
       </c>
       <c r="B8" t="n">
-        <v>1590.29</v>
+        <v>1464.71</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>1157.66</v>
+        <v>1064.91</v>
       </c>
       <c r="E8" t="n">
-        <v>314.59</v>
+        <v>292.57</v>
       </c>
       <c r="F8" t="n">
-        <v>2846</v>
+        <v>1293</v>
       </c>
       <c r="G8" t="n">
-        <v>425807</v>
+        <v>421546</v>
       </c>
       <c r="H8" t="n">
-        <v>73194</v>
+        <v>66810</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45782</v>
       </c>
       <c r="B9" t="n">
-        <v>626.28</v>
+        <v>647.62</v>
       </c>
       <c r="C9" t="n">
         <v>10.14</v>
       </c>
       <c r="D9" t="n">
-        <v>449.55</v>
+        <v>470.66</v>
       </c>
       <c r="E9" t="n">
-        <v>123.35</v>
+        <v>127.46</v>
       </c>
       <c r="F9" t="n">
-        <v>1093</v>
+        <v>863</v>
       </c>
       <c r="G9" t="n">
-        <v>168711</v>
+        <v>165686</v>
       </c>
       <c r="H9" t="n">
-        <v>27601</v>
+        <v>28748</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45783</v>
       </c>
       <c r="B10" t="n">
-        <v>1527.76</v>
+        <v>1532.61</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1105.39</v>
+        <v>1106.31</v>
       </c>
       <c r="E10" t="n">
-        <v>304.21</v>
+        <v>295.24</v>
       </c>
       <c r="F10" t="n">
-        <v>2565</v>
+        <v>1458</v>
       </c>
       <c r="G10" t="n">
-        <v>414261</v>
+        <v>369350</v>
       </c>
       <c r="H10" t="n">
-        <v>69687</v>
+        <v>66909</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45784</v>
       </c>
       <c r="B11" t="n">
-        <v>1404.15</v>
+        <v>1608</v>
       </c>
       <c r="C11" t="n">
-        <v>22.59</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1024.98</v>
+        <v>1158.85</v>
       </c>
       <c r="E11" t="n">
-        <v>282.53</v>
+        <v>318.74</v>
       </c>
       <c r="F11" t="n">
-        <v>2213</v>
+        <v>1394</v>
       </c>
       <c r="G11" t="n">
-        <v>402570</v>
+        <v>434668</v>
       </c>
       <c r="H11" t="n">
-        <v>64368</v>
+        <v>74144</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45785</v>
       </c>
       <c r="B12" t="n">
-        <v>1484.08</v>
+        <v>1472.44</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>23.13</v>
       </c>
       <c r="D12" t="n">
-        <v>1080.96</v>
+        <v>1066.7</v>
       </c>
       <c r="E12" t="n">
-        <v>304.15</v>
+        <v>287.05</v>
       </c>
       <c r="F12" t="n">
-        <v>2341</v>
+        <v>1675</v>
       </c>
       <c r="G12" t="n">
-        <v>392140</v>
+        <v>387808</v>
       </c>
       <c r="H12" t="n">
-        <v>67145</v>
+        <v>64511</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45786</v>
       </c>
       <c r="B13" t="n">
-        <v>1562.01</v>
+        <v>1405.01</v>
       </c>
       <c r="C13" t="n">
-        <v>23.83</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1134.17</v>
+        <v>1034.33</v>
       </c>
       <c r="E13" t="n">
-        <v>306.59</v>
+        <v>280.52</v>
       </c>
       <c r="F13" t="n">
-        <v>2757</v>
+        <v>1504</v>
       </c>
       <c r="G13" t="n">
-        <v>412647</v>
+        <v>387798</v>
       </c>
       <c r="H13" t="n">
-        <v>69501</v>
+        <v>63038</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45787</v>
       </c>
       <c r="B14" t="n">
-        <v>1523.97</v>
+        <v>1562.03</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1100.63</v>
+        <v>1139.65</v>
       </c>
       <c r="E14" t="n">
-        <v>301.51</v>
+        <v>309.6</v>
       </c>
       <c r="F14" t="n">
-        <v>2336</v>
+        <v>1434</v>
       </c>
       <c r="G14" t="n">
-        <v>399592</v>
+        <v>430783</v>
       </c>
       <c r="H14" t="n">
-        <v>70595</v>
+        <v>70393</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45788</v>
       </c>
       <c r="B15" t="n">
-        <v>1384.53</v>
+        <v>1590.97</v>
       </c>
       <c r="C15" t="n">
-        <v>23.36</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1005.07</v>
+        <v>1159.34</v>
       </c>
       <c r="E15" t="n">
-        <v>283.69</v>
+        <v>320.31</v>
       </c>
       <c r="F15" t="n">
-        <v>1936</v>
+        <v>1412</v>
       </c>
       <c r="G15" t="n">
-        <v>347527</v>
+        <v>403787</v>
       </c>
       <c r="H15" t="n">
-        <v>62946</v>
+        <v>71673</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45789</v>
       </c>
       <c r="B16" t="n">
-        <v>1501.05</v>
+        <v>1484.23</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1086.82</v>
+        <v>1072.41</v>
       </c>
       <c r="E16" t="n">
-        <v>300.67</v>
+        <v>294.72</v>
       </c>
       <c r="F16" t="n">
-        <v>2317</v>
+        <v>1216</v>
       </c>
       <c r="G16" t="n">
-        <v>380872</v>
+        <v>390941</v>
       </c>
       <c r="H16" t="n">
-        <v>68448</v>
+        <v>67726</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45790</v>
       </c>
       <c r="B17" t="n">
-        <v>1416.01</v>
+        <v>1461.15</v>
       </c>
       <c r="C17" t="n">
-        <v>22.36</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1026.69</v>
+        <v>1064.5</v>
       </c>
       <c r="E17" t="n">
-        <v>276.52</v>
+        <v>291.1</v>
       </c>
       <c r="F17" t="n">
-        <v>2278</v>
+        <v>1190</v>
       </c>
       <c r="G17" t="n">
-        <v>368659</v>
+        <v>404957</v>
       </c>
       <c r="H17" t="n">
-        <v>67910</v>
+        <v>66791</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45791</v>
       </c>
       <c r="B18" t="n">
-        <v>1449.81</v>
+        <v>1295.11</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>21.11</v>
       </c>
       <c r="D18" t="n">
-        <v>1051.66</v>
+        <v>933.13</v>
       </c>
       <c r="E18" t="n">
-        <v>282.71</v>
+        <v>264.01</v>
       </c>
       <c r="F18" t="n">
-        <v>2326</v>
+        <v>1206</v>
       </c>
       <c r="G18" t="n">
-        <v>393062</v>
+        <v>383326</v>
       </c>
       <c r="H18" t="n">
-        <v>64219</v>
+        <v>58464</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45792</v>
       </c>
       <c r="B19" t="n">
-        <v>1388.69</v>
+        <v>1551.76</v>
       </c>
       <c r="C19" t="n">
-        <v>21.27</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1005.67</v>
+        <v>1113.63</v>
       </c>
       <c r="E19" t="n">
-        <v>274.84</v>
+        <v>307.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1976</v>
+        <v>1349</v>
       </c>
       <c r="G19" t="n">
-        <v>359293</v>
+        <v>421809</v>
       </c>
       <c r="H19" t="n">
-        <v>63667</v>
+        <v>66336</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45793</v>
       </c>
       <c r="B20" t="n">
-        <v>1586.82</v>
+        <v>1386.53</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>22.37</v>
       </c>
       <c r="D20" t="n">
-        <v>1142.03</v>
+        <v>1010.37</v>
       </c>
       <c r="E20" t="n">
-        <v>312.93</v>
+        <v>276.12</v>
       </c>
       <c r="F20" t="n">
-        <v>2693</v>
+        <v>1093</v>
       </c>
       <c r="G20" t="n">
-        <v>406982</v>
+        <v>353818</v>
       </c>
       <c r="H20" t="n">
-        <v>72643</v>
+        <v>63305</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>1370.22</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>22.58</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>995.27</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>271.91</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2075</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>347137</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>62530</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45795</v>
       </c>
       <c r="B22" t="n">
-        <v>429.33</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>309.42</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>86.45</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>882</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>125941</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>19910</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45796</v>
       </c>
       <c r="B23" t="n">
-        <v>1098.93</v>
+        <v>1314.2</v>
       </c>
       <c r="C23" t="n">
-        <v>16.51</v>
+        <v>21.2</v>
       </c>
       <c r="D23" t="n">
-        <v>798.85</v>
+        <v>956.2</v>
       </c>
       <c r="E23" t="n">
-        <v>226.3</v>
+        <v>258.14</v>
       </c>
       <c r="F23" t="n">
-        <v>2246</v>
+        <v>1188</v>
       </c>
       <c r="G23" t="n">
-        <v>283987</v>
+        <v>334098</v>
       </c>
       <c r="H23" t="n">
-        <v>48578</v>
+        <v>59622</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45797</v>
       </c>
       <c r="B24" t="n">
-        <v>674.26</v>
+        <v>1425.96</v>
       </c>
       <c r="C24" t="n">
-        <v>11.43</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>490.9</v>
+        <v>1038.76</v>
       </c>
       <c r="E24" t="n">
-        <v>131.85</v>
+        <v>284.12</v>
       </c>
       <c r="F24" t="n">
-        <v>1139</v>
+        <v>1099</v>
       </c>
       <c r="G24" t="n">
-        <v>191186</v>
+        <v>386909</v>
       </c>
       <c r="H24" t="n">
-        <v>31788</v>
+        <v>62751</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45798</v>
       </c>
       <c r="B25" t="n">
-        <v>879.9</v>
+        <v>1465.86</v>
       </c>
       <c r="C25" t="n">
-        <v>13.45</v>
+        <v>23.56</v>
       </c>
       <c r="D25" t="n">
-        <v>638.23</v>
+        <v>1060.72</v>
       </c>
       <c r="E25" t="n">
-        <v>169.66</v>
+        <v>285.35</v>
       </c>
       <c r="F25" t="n">
-        <v>1844</v>
+        <v>1206</v>
       </c>
       <c r="G25" t="n">
-        <v>219692</v>
+        <v>410690</v>
       </c>
       <c r="H25" t="n">
-        <v>36793</v>
+        <v>64341</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45799</v>
       </c>
       <c r="B26" t="n">
-        <v>1440.06</v>
+        <v>1201.94</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>19.52</v>
       </c>
       <c r="D26" t="n">
-        <v>1043.89</v>
+        <v>868.33</v>
       </c>
       <c r="E26" t="n">
-        <v>278.74</v>
+        <v>243.07</v>
       </c>
       <c r="F26" t="n">
-        <v>2400</v>
+        <v>1047</v>
       </c>
       <c r="G26" t="n">
-        <v>357546</v>
+        <v>382212</v>
       </c>
       <c r="H26" t="n">
-        <v>66731</v>
+        <v>59076</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45800</v>
       </c>
       <c r="B27" t="n">
-        <v>607.21</v>
+        <v>1362.64</v>
       </c>
       <c r="C27" t="n">
-        <v>9.44</v>
+        <v>21.37</v>
       </c>
       <c r="D27" t="n">
-        <v>442.31</v>
+        <v>992.61</v>
       </c>
       <c r="E27" t="n">
-        <v>118.12</v>
+        <v>267.11</v>
       </c>
       <c r="F27" t="n">
-        <v>860</v>
+        <v>1382</v>
       </c>
       <c r="G27" t="n">
-        <v>166151</v>
+        <v>360377</v>
       </c>
       <c r="H27" t="n">
-        <v>27346</v>
+        <v>60223</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45801</v>
       </c>
       <c r="B28" t="n">
-        <v>1416.01</v>
+        <v>1560.41</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1027.18</v>
+        <v>1136.15</v>
       </c>
       <c r="E28" t="n">
-        <v>287.84</v>
+        <v>315.04</v>
       </c>
       <c r="F28" t="n">
-        <v>1986</v>
+        <v>1322</v>
       </c>
       <c r="G28" t="n">
-        <v>395746</v>
+        <v>405712</v>
       </c>
       <c r="H28" t="n">
-        <v>65451</v>
+        <v>71699</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45802</v>
       </c>
       <c r="B29" t="n">
-        <v>1275.16</v>
+        <v>1394.13</v>
       </c>
       <c r="C29" t="n">
-        <v>21.3</v>
+        <v>23.11</v>
       </c>
       <c r="D29" t="n">
-        <v>921.26</v>
+        <v>1016.25</v>
       </c>
       <c r="E29" t="n">
-        <v>258.79</v>
+        <v>278.55</v>
       </c>
       <c r="F29" t="n">
-        <v>2048</v>
+        <v>1008</v>
       </c>
       <c r="G29" t="n">
-        <v>343495</v>
+        <v>356499</v>
       </c>
       <c r="H29" t="n">
-        <v>60156</v>
+        <v>63992</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45803</v>
       </c>
       <c r="B30" t="n">
-        <v>1445.88</v>
+        <v>1555.7</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1055.13</v>
+        <v>1119.1</v>
       </c>
       <c r="E30" t="n">
-        <v>276.71</v>
+        <v>315.33</v>
       </c>
       <c r="F30" t="n">
-        <v>2053</v>
+        <v>1530</v>
       </c>
       <c r="G30" t="n">
-        <v>377533</v>
+        <v>413323</v>
       </c>
       <c r="H30" t="n">
-        <v>63423</v>
+        <v>73334</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45804</v>
       </c>
       <c r="B31" t="n">
-        <v>1268.18</v>
+        <v>1495.27</v>
       </c>
       <c r="C31" t="n">
-        <v>19.75</v>
+        <v>23.77</v>
       </c>
       <c r="D31" t="n">
-        <v>915.5599999999999</v>
+        <v>1089.46</v>
       </c>
       <c r="E31" t="n">
-        <v>252.32</v>
+        <v>299.46</v>
       </c>
       <c r="F31" t="n">
-        <v>2745</v>
+        <v>1507</v>
       </c>
       <c r="G31" t="n">
-        <v>333155</v>
+        <v>379433</v>
       </c>
       <c r="H31" t="n">
-        <v>59370</v>
+        <v>71565</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45805</v>
       </c>
       <c r="B32" t="n">
-        <v>1017.79</v>
+        <v>1579.1</v>
       </c>
       <c r="C32" t="n">
-        <v>16.74</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>738</v>
+        <v>1149.62</v>
       </c>
       <c r="E32" t="n">
-        <v>204.6</v>
+        <v>314.25</v>
       </c>
       <c r="F32" t="n">
-        <v>2132</v>
+        <v>2276</v>
       </c>
       <c r="G32" t="n">
-        <v>296307</v>
+        <v>375736</v>
       </c>
       <c r="H32" t="n">
-        <v>44615</v>
+        <v>67911</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45806</v>
       </c>
       <c r="B33" t="n">
-        <v>1449.93</v>
+        <v>1484.08</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>1044.27</v>
+        <v>1080.96</v>
       </c>
       <c r="E33" t="n">
-        <v>290.87</v>
+        <v>304.15</v>
       </c>
       <c r="F33" t="n">
-        <v>2148</v>
+        <v>1436</v>
       </c>
       <c r="G33" t="n">
-        <v>400055</v>
+        <v>392140</v>
       </c>
       <c r="H33" t="n">
-        <v>65839</v>
+        <v>67145</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45807</v>
       </c>
       <c r="B34" t="n">
-        <v>1526.53</v>
+        <v>1562.01</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>23.83</v>
       </c>
       <c r="D34" t="n">
-        <v>1112.61</v>
+        <v>1134.17</v>
       </c>
       <c r="E34" t="n">
-        <v>309.31</v>
+        <v>306.59</v>
       </c>
       <c r="F34" t="n">
-        <v>2100</v>
+        <v>1691</v>
       </c>
       <c r="G34" t="n">
-        <v>384257</v>
+        <v>412647</v>
       </c>
       <c r="H34" t="n">
-        <v>72974</v>
+        <v>69501</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45808</v>
       </c>
       <c r="B35" t="n">
-        <v>937.9400000000001</v>
+        <v>1194.45</v>
       </c>
       <c r="C35" t="n">
-        <v>16.59</v>
+        <v>18.81</v>
       </c>
       <c r="D35" t="n">
-        <v>678.34</v>
+        <v>862.65</v>
       </c>
       <c r="E35" t="n">
-        <v>183.31</v>
+        <v>236.32</v>
       </c>
       <c r="F35" t="n">
-        <v>1699</v>
+        <v>1404</v>
       </c>
       <c r="G35" t="n">
-        <v>278089</v>
+        <v>322170</v>
       </c>
       <c r="H35" t="n">
-        <v>43689</v>
+        <v>55330</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>39750.69</v>
+        <v>41391.39</v>
       </c>
       <c r="C37" t="n">
-        <v>638.51</v>
+        <v>659.54</v>
       </c>
       <c r="D37" t="n">
-        <v>28812.5</v>
+        <v>30046.74</v>
       </c>
       <c r="E37" t="n">
-        <v>7908.660000000001</v>
+        <v>8225.710000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>65424</v>
+        <v>38893</v>
       </c>
       <c r="G37" t="n">
-        <v>10570049</v>
+        <v>10976952</v>
       </c>
       <c r="H37" t="n">
-        <v>1814912</v>
+        <v>1877154</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_05.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_05.xlsx
@@ -480,25 +480,25 @@
         <v>45778</v>
       </c>
       <c r="B5" t="n">
-        <v>1327.08</v>
+        <v>1382.51</v>
       </c>
       <c r="C5" t="n">
-        <v>23.62</v>
+        <v>22.98</v>
       </c>
       <c r="D5" t="n">
-        <v>966.12</v>
+        <v>997.42</v>
       </c>
       <c r="E5" t="n">
-        <v>264.98</v>
+        <v>273.76</v>
       </c>
       <c r="F5" t="n">
-        <v>1162</v>
+        <v>1266</v>
       </c>
       <c r="G5" t="n">
-        <v>339259</v>
+        <v>383317</v>
       </c>
       <c r="H5" t="n">
-        <v>59529</v>
+        <v>61489</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45779</v>
       </c>
       <c r="B6" t="n">
-        <v>1537.91</v>
+        <v>991.12</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>15.99</v>
       </c>
       <c r="D6" t="n">
-        <v>1109.92</v>
+        <v>713.96</v>
       </c>
       <c r="E6" t="n">
-        <v>298.53</v>
+        <v>193.37</v>
       </c>
       <c r="F6" t="n">
-        <v>1426</v>
+        <v>1322</v>
       </c>
       <c r="G6" t="n">
-        <v>381251</v>
+        <v>261209</v>
       </c>
       <c r="H6" t="n">
-        <v>73295</v>
+        <v>43673</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45780</v>
       </c>
       <c r="B7" t="n">
-        <v>1468.48</v>
+        <v>1414.62</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>23.01</v>
       </c>
       <c r="D7" t="n">
-        <v>1070.93</v>
+        <v>1020.43</v>
       </c>
       <c r="E7" t="n">
-        <v>290.08</v>
+        <v>280.56</v>
       </c>
       <c r="F7" t="n">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="G7" t="n">
-        <v>368219</v>
+        <v>410162</v>
       </c>
       <c r="H7" t="n">
-        <v>68992</v>
+        <v>67131</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45781</v>
       </c>
       <c r="B8" t="n">
-        <v>1464.71</v>
+        <v>1356.5</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>21.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1064.91</v>
+        <v>979.4400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>292.57</v>
+        <v>282.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1293</v>
+        <v>1275</v>
       </c>
       <c r="G8" t="n">
-        <v>421546</v>
+        <v>346969</v>
       </c>
       <c r="H8" t="n">
-        <v>66810</v>
+        <v>62790</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45782</v>
       </c>
       <c r="B9" t="n">
-        <v>647.62</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>10.14</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>470.66</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>127.46</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>863</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>165686</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>28748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45783</v>
       </c>
       <c r="B10" t="n">
-        <v>1532.61</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1106.31</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>295.24</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1458</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>369350</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>66909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45784</v>
       </c>
       <c r="B11" t="n">
-        <v>1608</v>
+        <v>1375.14</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>21.25</v>
       </c>
       <c r="D11" t="n">
-        <v>1158.85</v>
+        <v>1005.55</v>
       </c>
       <c r="E11" t="n">
-        <v>318.74</v>
+        <v>274.84</v>
       </c>
       <c r="F11" t="n">
-        <v>1394</v>
+        <v>1285</v>
       </c>
       <c r="G11" t="n">
-        <v>434668</v>
+        <v>367419</v>
       </c>
       <c r="H11" t="n">
-        <v>74144</v>
+        <v>67650</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45785</v>
       </c>
       <c r="B12" t="n">
-        <v>1472.44</v>
+        <v>1401.53</v>
       </c>
       <c r="C12" t="n">
-        <v>23.13</v>
+        <v>23.89</v>
       </c>
       <c r="D12" t="n">
-        <v>1066.7</v>
+        <v>1007.83</v>
       </c>
       <c r="E12" t="n">
-        <v>287.05</v>
+        <v>290.46</v>
       </c>
       <c r="F12" t="n">
-        <v>1675</v>
+        <v>1584</v>
       </c>
       <c r="G12" t="n">
-        <v>387808</v>
+        <v>383352</v>
       </c>
       <c r="H12" t="n">
-        <v>64511</v>
+        <v>65050</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45786</v>
       </c>
       <c r="B13" t="n">
-        <v>1405.01</v>
+        <v>1458.09</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1034.33</v>
+        <v>1072.59</v>
       </c>
       <c r="E13" t="n">
-        <v>280.52</v>
+        <v>283.24</v>
       </c>
       <c r="F13" t="n">
-        <v>1504</v>
+        <v>1469</v>
       </c>
       <c r="G13" t="n">
-        <v>387798</v>
+        <v>365040</v>
       </c>
       <c r="H13" t="n">
-        <v>63038</v>
+        <v>70492</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45787</v>
       </c>
       <c r="B14" t="n">
-        <v>1562.03</v>
+        <v>1554.64</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1139.65</v>
+        <v>1131.17</v>
       </c>
       <c r="E14" t="n">
-        <v>309.6</v>
+        <v>308.28</v>
       </c>
       <c r="F14" t="n">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="G14" t="n">
-        <v>430783</v>
+        <v>421631</v>
       </c>
       <c r="H14" t="n">
-        <v>70393</v>
+        <v>70202</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45788</v>
       </c>
       <c r="B15" t="n">
-        <v>1590.97</v>
+        <v>1408.72</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>22.64</v>
       </c>
       <c r="D15" t="n">
-        <v>1159.34</v>
+        <v>1015.87</v>
       </c>
       <c r="E15" t="n">
-        <v>320.31</v>
+        <v>280.46</v>
       </c>
       <c r="F15" t="n">
-        <v>1412</v>
+        <v>1603</v>
       </c>
       <c r="G15" t="n">
-        <v>403787</v>
+        <v>338279</v>
       </c>
       <c r="H15" t="n">
-        <v>71673</v>
+        <v>67909</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45789</v>
       </c>
       <c r="B16" t="n">
-        <v>1484.23</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1072.41</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>294.72</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>390941</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>67726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45790</v>
       </c>
       <c r="B17" t="n">
-        <v>1461.15</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1064.5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>291.1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1190</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>404957</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>66791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45791</v>
       </c>
       <c r="B18" t="n">
-        <v>1295.11</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>21.11</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>933.13</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>264.01</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>383326</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>58464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45792</v>
       </c>
       <c r="B19" t="n">
-        <v>1551.76</v>
+        <v>1484.11</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1113.63</v>
+        <v>1082.93</v>
       </c>
       <c r="E19" t="n">
-        <v>307.2</v>
+        <v>291.06</v>
       </c>
       <c r="F19" t="n">
-        <v>1349</v>
+        <v>1850</v>
       </c>
       <c r="G19" t="n">
-        <v>421809</v>
+        <v>432604</v>
       </c>
       <c r="H19" t="n">
-        <v>66336</v>
+        <v>68201</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45793</v>
       </c>
       <c r="B20" t="n">
-        <v>1386.53</v>
+        <v>1261.41</v>
       </c>
       <c r="C20" t="n">
-        <v>22.37</v>
+        <v>19.58</v>
       </c>
       <c r="D20" t="n">
-        <v>1010.37</v>
+        <v>909.14</v>
       </c>
       <c r="E20" t="n">
-        <v>276.12</v>
+        <v>250.37</v>
       </c>
       <c r="F20" t="n">
-        <v>1093</v>
+        <v>1285</v>
       </c>
       <c r="G20" t="n">
-        <v>353818</v>
+        <v>343967</v>
       </c>
       <c r="H20" t="n">
-        <v>63305</v>
+        <v>56831</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45794</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1523.81</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1102.35</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>299.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>440269</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>69462</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45795</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1528.1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1116.63</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>296.46</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>409267</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>67912</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45796</v>
       </c>
       <c r="B23" t="n">
-        <v>1314.2</v>
+        <v>1444.07</v>
       </c>
       <c r="C23" t="n">
-        <v>21.2</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>956.2</v>
+        <v>1037.09</v>
       </c>
       <c r="E23" t="n">
-        <v>258.14</v>
+        <v>292.33</v>
       </c>
       <c r="F23" t="n">
-        <v>1188</v>
+        <v>1336</v>
       </c>
       <c r="G23" t="n">
-        <v>334098</v>
+        <v>385197</v>
       </c>
       <c r="H23" t="n">
-        <v>59622</v>
+        <v>66751</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45797</v>
       </c>
       <c r="B24" t="n">
-        <v>1425.96</v>
+        <v>1466.1</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>1038.76</v>
+        <v>1058.96</v>
       </c>
       <c r="E24" t="n">
-        <v>284.12</v>
+        <v>284.79</v>
       </c>
       <c r="F24" t="n">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="G24" t="n">
-        <v>386909</v>
+        <v>401430</v>
       </c>
       <c r="H24" t="n">
-        <v>62751</v>
+        <v>65014</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45798</v>
       </c>
       <c r="B25" t="n">
-        <v>1465.86</v>
+        <v>1474.28</v>
       </c>
       <c r="C25" t="n">
-        <v>23.56</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1060.72</v>
+        <v>1070.17</v>
       </c>
       <c r="E25" t="n">
-        <v>285.35</v>
+        <v>302.06</v>
       </c>
       <c r="F25" t="n">
-        <v>1206</v>
+        <v>1043</v>
       </c>
       <c r="G25" t="n">
-        <v>410690</v>
+        <v>373017</v>
       </c>
       <c r="H25" t="n">
-        <v>64341</v>
+        <v>64815</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45799</v>
       </c>
       <c r="B26" t="n">
-        <v>1201.94</v>
+        <v>1378.91</v>
       </c>
       <c r="C26" t="n">
-        <v>19.52</v>
+        <v>21.78</v>
       </c>
       <c r="D26" t="n">
-        <v>868.33</v>
+        <v>997.3</v>
       </c>
       <c r="E26" t="n">
-        <v>243.07</v>
+        <v>268.53</v>
       </c>
       <c r="F26" t="n">
-        <v>1047</v>
+        <v>1143</v>
       </c>
       <c r="G26" t="n">
-        <v>382212</v>
+        <v>357619</v>
       </c>
       <c r="H26" t="n">
-        <v>59076</v>
+        <v>62389</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45800</v>
       </c>
       <c r="B27" t="n">
-        <v>1362.64</v>
+        <v>1256.9</v>
       </c>
       <c r="C27" t="n">
-        <v>21.37</v>
+        <v>19.39</v>
       </c>
       <c r="D27" t="n">
-        <v>992.61</v>
+        <v>906.54</v>
       </c>
       <c r="E27" t="n">
-        <v>267.11</v>
+        <v>245.48</v>
       </c>
       <c r="F27" t="n">
-        <v>1382</v>
+        <v>1331</v>
       </c>
       <c r="G27" t="n">
-        <v>360377</v>
+        <v>367653</v>
       </c>
       <c r="H27" t="n">
-        <v>60223</v>
+        <v>58066</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45801</v>
       </c>
       <c r="B28" t="n">
-        <v>1560.41</v>
+        <v>1532.03</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1136.15</v>
+        <v>1112.92</v>
       </c>
       <c r="E28" t="n">
-        <v>315.04</v>
+        <v>310.68</v>
       </c>
       <c r="F28" t="n">
-        <v>1322</v>
+        <v>1139</v>
       </c>
       <c r="G28" t="n">
-        <v>405712</v>
+        <v>410767</v>
       </c>
       <c r="H28" t="n">
-        <v>71699</v>
+        <v>71330</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45802</v>
       </c>
       <c r="B29" t="n">
-        <v>1394.13</v>
+        <v>1448.13</v>
       </c>
       <c r="C29" t="n">
-        <v>23.11</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>1016.25</v>
+        <v>1046.98</v>
       </c>
       <c r="E29" t="n">
-        <v>278.55</v>
+        <v>293.59</v>
       </c>
       <c r="F29" t="n">
-        <v>1008</v>
+        <v>1032</v>
       </c>
       <c r="G29" t="n">
-        <v>356499</v>
+        <v>385701</v>
       </c>
       <c r="H29" t="n">
-        <v>63992</v>
+        <v>66466</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45803</v>
       </c>
       <c r="B30" t="n">
-        <v>1555.7</v>
+        <v>1216.02</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>20.8</v>
       </c>
       <c r="D30" t="n">
-        <v>1119.1</v>
+        <v>880.05</v>
       </c>
       <c r="E30" t="n">
-        <v>315.33</v>
+        <v>236.74</v>
       </c>
       <c r="F30" t="n">
-        <v>1530</v>
+        <v>1260</v>
       </c>
       <c r="G30" t="n">
-        <v>413323</v>
+        <v>326990</v>
       </c>
       <c r="H30" t="n">
-        <v>73334</v>
+        <v>51997</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45804</v>
       </c>
       <c r="B31" t="n">
-        <v>1495.27</v>
+        <v>1347.55</v>
       </c>
       <c r="C31" t="n">
-        <v>23.77</v>
+        <v>22.69</v>
       </c>
       <c r="D31" t="n">
-        <v>1089.46</v>
+        <v>976.1799999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>299.46</v>
+        <v>266.68</v>
       </c>
       <c r="F31" t="n">
-        <v>1507</v>
+        <v>1439</v>
       </c>
       <c r="G31" t="n">
-        <v>379433</v>
+        <v>356276</v>
       </c>
       <c r="H31" t="n">
-        <v>71565</v>
+        <v>63517</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45805</v>
       </c>
       <c r="B32" t="n">
-        <v>1579.1</v>
+        <v>1517.82</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1149.62</v>
+        <v>1106.78</v>
       </c>
       <c r="E32" t="n">
-        <v>314.25</v>
+        <v>296.61</v>
       </c>
       <c r="F32" t="n">
-        <v>2276</v>
+        <v>1561</v>
       </c>
       <c r="G32" t="n">
-        <v>375736</v>
+        <v>399791</v>
       </c>
       <c r="H32" t="n">
-        <v>67911</v>
+        <v>68519</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45806</v>
       </c>
       <c r="B33" t="n">
-        <v>1484.08</v>
+        <v>1427.63</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>23.82</v>
       </c>
       <c r="D33" t="n">
-        <v>1080.96</v>
+        <v>1035.44</v>
       </c>
       <c r="E33" t="n">
-        <v>304.15</v>
+        <v>281.61</v>
       </c>
       <c r="F33" t="n">
-        <v>1436</v>
+        <v>1420</v>
       </c>
       <c r="G33" t="n">
-        <v>392140</v>
+        <v>386409</v>
       </c>
       <c r="H33" t="n">
-        <v>67145</v>
+        <v>68085</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45807</v>
       </c>
       <c r="B34" t="n">
-        <v>1562.01</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>23.83</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1134.17</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>306.59</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1691</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>412647</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>69501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45808</v>
       </c>
       <c r="B35" t="n">
-        <v>1194.45</v>
+        <v>1532.99</v>
       </c>
       <c r="C35" t="n">
-        <v>18.81</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>862.65</v>
+        <v>1109.6</v>
       </c>
       <c r="E35" t="n">
-        <v>236.32</v>
+        <v>308.72</v>
       </c>
       <c r="F35" t="n">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="G35" t="n">
-        <v>322170</v>
+        <v>393368</v>
       </c>
       <c r="H35" t="n">
-        <v>55330</v>
+        <v>71049</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41391.39</v>
+        <v>35182.73</v>
       </c>
       <c r="C37" t="n">
-        <v>659.54</v>
+        <v>567.58</v>
       </c>
       <c r="D37" t="n">
-        <v>30046.74</v>
+        <v>25493.32</v>
       </c>
       <c r="E37" t="n">
-        <v>8225.710000000001</v>
+        <v>6991.719999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>38893</v>
+        <v>33576</v>
       </c>
       <c r="G37" t="n">
-        <v>10976952</v>
+        <v>9447703</v>
       </c>
       <c r="H37" t="n">
-        <v>1877154</v>
+        <v>1616790</v>
       </c>
     </row>
   </sheetData>
